--- a/output/01_Aviat_213종_정규화.xlsx
+++ b/output/01_Aviat_213종_정규화.xlsx
@@ -18472,7 +18472,7 @@
       </c>
       <c r="E16" s="8" t="inlineStr">
         <is>
-          <t>IDU/Chassis</t>
+          <t>기타</t>
         </is>
       </c>
       <c r="F16" s="8" t="inlineStr">
@@ -18562,7 +18562,7 @@
       </c>
       <c r="E18" s="8" t="inlineStr">
         <is>
-          <t>Interface Card</t>
+          <t>Cable</t>
         </is>
       </c>
       <c r="F18" s="8" t="inlineStr"/>
@@ -19674,7 +19674,7 @@
       </c>
       <c r="E42" s="8" t="inlineStr">
         <is>
-          <t>Interface Card</t>
+          <t>Cable</t>
         </is>
       </c>
       <c r="F42" s="8" t="inlineStr"/>
@@ -20954,7 +20954,7 @@
       </c>
       <c r="E66" s="8" t="inlineStr">
         <is>
-          <t>Interface Card</t>
+          <t>Cable</t>
         </is>
       </c>
       <c r="F66" s="8" t="inlineStr"/>
@@ -21799,7 +21799,7 @@
       </c>
       <c r="E83" s="8" t="inlineStr">
         <is>
-          <t>Interface Card</t>
+          <t>Cable</t>
         </is>
       </c>
       <c r="F83" s="8" t="inlineStr">
@@ -24304,7 +24304,7 @@
       </c>
       <c r="E132" s="8" t="inlineStr">
         <is>
-          <t>Interface Card</t>
+          <t>IDU/Chassis</t>
         </is>
       </c>
       <c r="F132" s="8" t="inlineStr">
@@ -24971,7 +24971,7 @@
       </c>
       <c r="E147" s="8" t="inlineStr">
         <is>
-          <t>Interface Card</t>
+          <t>IDU/Chassis</t>
         </is>
       </c>
       <c r="F147" s="8" t="inlineStr">
@@ -25065,7 +25065,7 @@
       </c>
       <c r="E149" s="8" t="inlineStr">
         <is>
-          <t>Interface Card</t>
+          <t>IDU/Chassis</t>
         </is>
       </c>
       <c r="F149" s="8" t="inlineStr">
@@ -26395,7 +26395,7 @@
       </c>
       <c r="E179" s="8" t="inlineStr">
         <is>
-          <t>Interface Card</t>
+          <t>Cable</t>
         </is>
       </c>
       <c r="F179" s="8" t="inlineStr">
@@ -28570,19 +28570,19 @@
         </is>
       </c>
       <c r="B4" s="8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>3</v>
+        <v>71</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>4500000</v>
+        <v>263997096</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>4410000</v>
+        <v>258477128</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>0.02386115598635793</v>
+        <v>0.02307546550804345</v>
       </c>
     </row>
     <row r="5">
@@ -28658,19 +28658,19 @@
         </is>
       </c>
       <c r="B8" s="8" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>190</v>
+        <v>112</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>373018886</v>
+        <v>111526540</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>365318520</v>
+        <v>109296042</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>0.04152621194070127</v>
+        <v>0.04511756446825942</v>
       </c>
     </row>
     <row r="9">
@@ -28878,19 +28878,19 @@
         </is>
       </c>
       <c r="B18" s="8" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>444</v>
+        <v>454</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>61108000</v>
+        <v>63103250</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>59466400</v>
+        <v>61421750</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>0.02913413413413414</v>
+        <v>0.03260925931129395</v>
       </c>
     </row>
     <row r="19">
@@ -29032,7 +29032,7 @@
         </is>
       </c>
       <c r="B25" s="8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>92</v>
@@ -29044,7 +29044,7 @@
         <v>7922760</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>0.0275628753364076</v>
+        <v>0.02759357568517477</v>
       </c>
     </row>
     <row r="26">
